--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.07621927483072</v>
+        <v>13.17488563215999</v>
       </c>
       <c r="D2" t="n">
-        <v>80.69347983238031</v>
+        <v>13.1126904727618</v>
       </c>
       <c r="E2" t="n">
-        <v>10.30976597671153</v>
+        <v>1.675336971215623</v>
       </c>
       <c r="F2" t="n">
-        <v>10.30565997523669</v>
+        <v>1.674669745975963</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.63988274816438</v>
+        <v>10.82898094657671</v>
       </c>
       <c r="D3" t="n">
-        <v>66.19574975398113</v>
+        <v>10.75680933502193</v>
       </c>
       <c r="E3" t="n">
-        <v>10.30976597671153</v>
+        <v>1.675336971215623</v>
       </c>
       <c r="F3" t="n">
-        <v>10.30565997523669</v>
+        <v>1.674669745975963</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.74267873570253</v>
+        <v>11.00818529455166</v>
       </c>
       <c r="D4" t="n">
-        <v>67.20716707647553</v>
+        <v>10.92116464992727</v>
       </c>
       <c r="E4" t="n">
-        <v>10.30976597671153</v>
+        <v>1.675336971215623</v>
       </c>
       <c r="F4" t="n">
-        <v>10.30565997523669</v>
+        <v>1.674669745975963</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.95238979791361</v>
+        <v>8.442263342160961</v>
       </c>
       <c r="D5" t="n">
-        <v>51.5733037373048</v>
+        <v>8.380661857312029</v>
       </c>
       <c r="E5" t="n">
-        <v>10.30976597671153</v>
+        <v>1.675336971215623</v>
       </c>
       <c r="F5" t="n">
-        <v>10.30565997523669</v>
+        <v>1.674669745975963</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
